--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-diffusion.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-diffusion.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01</t>
+    <t>2026-09-02</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-diffusion.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-diffusion.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-diffusion.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-diffusion.xlsx
@@ -884,7 +884,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
   &lt;code value="36421003"/&gt;
   &lt;display value="Carbon monoxide diffusing capacity measurement (procedure)"/&gt;
 &lt;/valueCoding&gt;</t>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-diffusion.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-diffusion.xlsx
@@ -1204,6 +1204,26 @@
 </t>
   </si>
   <si>
+    <t>DiagnosticReport.result:IRV_ERV</t>
+  </si>
+  <si>
+    <t>IRV_ERV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-irv-erv)
+</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.result:TLC</t>
+  </si>
+  <si>
+    <t>TLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-tlc)
+</t>
+  </si>
+  <si>
     <t>DiagnosticReport.result:RV</t>
   </si>
   <si>
@@ -1214,30 +1234,10 @@
 </t>
   </si>
   <si>
-    <t>DiagnosticReport.result:TLC</t>
-  </si>
-  <si>
-    <t>TLC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-tlc)
-</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.result:RVL</t>
-  </si>
-  <si>
-    <t>RVL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-rvl)
-</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.result:RVL_TLC</t>
-  </si>
-  <si>
-    <t>RVL_TLC</t>
+    <t>DiagnosticReport.result:RV_TLC</t>
+  </si>
+  <si>
+    <t>RV_TLC</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-lungenfunktion/StructureDefinition/mii-pr-lungenfunktion-rvl-tlc)
@@ -1788,7 +1788,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="106.44140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="107.06640625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-diffusion.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-diffusion.xlsx
@@ -815,6 +815,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
   &lt;code value="720449003"/&gt;
   &lt;display value="Pulmonary function report (record artifact)"/&gt;
 &lt;/valueCoding&gt;</t>
@@ -884,7 +885,7 @@
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
-  &lt;version value="http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
   &lt;code value="36421003"/&gt;
   &lt;display value="Carbon monoxide diffusing capacity measurement (procedure)"/&gt;
 &lt;/valueCoding&gt;</t>
@@ -1432,7 +1433,7 @@
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://snomed.info/sct"/&gt;
+  &lt;system value="http://snomed.info/sct|http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
